--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/108.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/108.xlsx
@@ -426,13 +426,13 @@
         <v>-25.17158543895859</v>
       </c>
       <c r="E2">
-        <v>-13.8194692218571</v>
+        <v>-10.8226655062751</v>
       </c>
       <c r="F2">
-        <v>-2.108582034949357</v>
+        <v>-2.43451727182667</v>
       </c>
       <c r="G2">
-        <v>-9.260543840034076</v>
+        <v>-7.079529954397904</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-25.07809180032529</v>
       </c>
       <c r="E3">
-        <v>-14.50745310699841</v>
+        <v>-11.86899206811737</v>
       </c>
       <c r="F3">
-        <v>-2.521596081576357</v>
+        <v>-2.618775175068378</v>
       </c>
       <c r="G3">
-        <v>-9.661550221205994</v>
+        <v>-6.805072487010165</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-24.7764107956308</v>
       </c>
       <c r="E4">
-        <v>-13.28520891538017</v>
+        <v>-11.46733453753304</v>
       </c>
       <c r="F4">
-        <v>-2.130951268294555</v>
+        <v>-2.681013731510316</v>
       </c>
       <c r="G4">
-        <v>-7.93655736251335</v>
+        <v>-6.997170202471914</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-24.25213393257429</v>
       </c>
       <c r="E5">
-        <v>-15.8185142593291</v>
+        <v>-12.02377078122554</v>
       </c>
       <c r="F5">
-        <v>-2.143154776872597</v>
+        <v>-2.638108441882316</v>
       </c>
       <c r="G5">
-        <v>-8.229967703113417</v>
+        <v>-7.006254339431675</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-23.49060645714506</v>
       </c>
       <c r="E6">
-        <v>-15.74150303035465</v>
+        <v>-13.42654711763357</v>
       </c>
       <c r="F6">
-        <v>-2.527169337462392</v>
+        <v>-2.434615847547603</v>
       </c>
       <c r="G6">
-        <v>-7.943539303055672</v>
+        <v>-6.283588732573089</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.52431723507137</v>
       </c>
       <c r="E7">
-        <v>-15.61244604961006</v>
+        <v>-13.77128172994148</v>
       </c>
       <c r="F7">
-        <v>-2.466718397875695</v>
+        <v>-2.159594556348556</v>
       </c>
       <c r="G7">
-        <v>-7.682247875277616</v>
+        <v>-6.104597466901314</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.39093488449437</v>
       </c>
       <c r="E8">
-        <v>-16.85162673401699</v>
+        <v>-14.85788001113397</v>
       </c>
       <c r="F8">
-        <v>-2.013705802837118</v>
+        <v>-2.185000584592417</v>
       </c>
       <c r="G8">
-        <v>-7.61541127138527</v>
+        <v>-5.277424558459015</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.11403717845805</v>
       </c>
       <c r="E9">
-        <v>-16.19635654510709</v>
+        <v>-13.98853979893347</v>
       </c>
       <c r="F9">
-        <v>-2.969264878499474</v>
+        <v>-2.642830964445676</v>
       </c>
       <c r="G9">
-        <v>-7.524410995601784</v>
+        <v>-5.283837085168583</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.7345888533292</v>
       </c>
       <c r="E10">
-        <v>-17.98193837480552</v>
+        <v>-15.62069240077802</v>
       </c>
       <c r="F10">
-        <v>-2.309997083837848</v>
+        <v>-2.828497920639546</v>
       </c>
       <c r="G10">
-        <v>-6.719488263728926</v>
+        <v>-4.751786069370154</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.31564472467285</v>
       </c>
       <c r="E11">
-        <v>-17.96481168610851</v>
+        <v>-15.3263687611235</v>
       </c>
       <c r="F11">
-        <v>-2.1728931666331</v>
+        <v>-2.516254768563106</v>
       </c>
       <c r="G11">
-        <v>-6.44820229896781</v>
+        <v>-4.118107926607177</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.89784264486022</v>
       </c>
       <c r="E12">
-        <v>-19.69496499395305</v>
+        <v>-16.24340286157278</v>
       </c>
       <c r="F12">
-        <v>-1.46777192275691</v>
+        <v>-2.825172025517306</v>
       </c>
       <c r="G12">
-        <v>-6.030249235180362</v>
+        <v>-3.863748781188354</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.51159701897204</v>
       </c>
       <c r="E13">
-        <v>-19.71738094029102</v>
+        <v>-16.46618114038012</v>
       </c>
       <c r="F13">
-        <v>-2.084724225381328</v>
+        <v>-2.420852523150089</v>
       </c>
       <c r="G13">
-        <v>-5.538596806597658</v>
+        <v>-3.225733823768933</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.22940857201106</v>
       </c>
       <c r="E14">
-        <v>-20.23359074937338</v>
+        <v>-18.07921905343829</v>
       </c>
       <c r="F14">
-        <v>-2.071967367378216</v>
+        <v>-2.390249317821064</v>
       </c>
       <c r="G14">
-        <v>-5.141937171718802</v>
+        <v>-3.569550530749941</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.09045570838511</v>
       </c>
       <c r="E15">
-        <v>-21.4465515692759</v>
+        <v>-17.54773923000207</v>
       </c>
       <c r="F15">
-        <v>-2.259699443507265</v>
+        <v>-2.376117369929305</v>
       </c>
       <c r="G15">
-        <v>-4.598312488715081</v>
+        <v>-2.963035414136685</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.11079878010471</v>
       </c>
       <c r="E16">
-        <v>-21.90308061941117</v>
+        <v>-19.19888425183479</v>
       </c>
       <c r="F16">
-        <v>-1.793062689794845</v>
+        <v>-2.226509246779298</v>
       </c>
       <c r="G16">
-        <v>-4.890491306374538</v>
+        <v>-2.063580054389939</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.33411376287335</v>
       </c>
       <c r="E17">
-        <v>-22.02345198700906</v>
+        <v>-19.58625444692492</v>
       </c>
       <c r="F17">
-        <v>-2.154637605810204</v>
+        <v>-2.195626881635529</v>
       </c>
       <c r="G17">
-        <v>-4.029315784698385</v>
+        <v>-1.65885262003188</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.773717241046178</v>
       </c>
       <c r="E18">
-        <v>-22.59355063678269</v>
+        <v>-20.5899001412449</v>
       </c>
       <c r="F18">
-        <v>-1.669217621239305</v>
+        <v>-2.172876599285043</v>
       </c>
       <c r="G18">
-        <v>-2.928916931808956</v>
+        <v>-1.354408231149423</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.408003160588894</v>
       </c>
       <c r="E19">
-        <v>-23.29706265929631</v>
+        <v>-19.99322840599425</v>
       </c>
       <c r="F19">
-        <v>-1.090839903461051</v>
+        <v>-2.455314263841355</v>
       </c>
       <c r="G19">
-        <v>-3.287879384632131</v>
+        <v>-1.325318467495847</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.231080463378476</v>
       </c>
       <c r="E20">
-        <v>-25.29125770110609</v>
+        <v>-21.94273193782233</v>
       </c>
       <c r="F20">
-        <v>-1.178150656083521</v>
+        <v>-1.445797820662847</v>
       </c>
       <c r="G20">
-        <v>-3.407688027698355</v>
+        <v>-1.02455209470752</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.225483965444161</v>
       </c>
       <c r="E21">
-        <v>-24.62800834099467</v>
+        <v>-22.15416186076645</v>
       </c>
       <c r="F21">
-        <v>-0.7747746641880937</v>
+        <v>-1.406408950659731</v>
       </c>
       <c r="G21">
-        <v>-3.256187532184688</v>
+        <v>-1.175605666573386</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.34756807776664</v>
       </c>
       <c r="E22">
-        <v>-23.76303357773757</v>
+        <v>-23.95943802392424</v>
       </c>
       <c r="F22">
-        <v>-0.9357811228006224</v>
+        <v>-1.241802407314635</v>
       </c>
       <c r="G22">
-        <v>-2.369037470207413</v>
+        <v>-0.06867510733497542</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.558913962220686</v>
       </c>
       <c r="E23">
-        <v>-26.19658569624554</v>
+        <v>-23.47004583791531</v>
       </c>
       <c r="F23">
-        <v>-1.29048473120976</v>
+        <v>-1.140028359839285</v>
       </c>
       <c r="G23">
-        <v>-3.331495822112029</v>
+        <v>-0.7680576474158671</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.83526521251258</v>
       </c>
       <c r="E24">
-        <v>-27.58058245094376</v>
+        <v>-23.42125605895667</v>
       </c>
       <c r="F24">
-        <v>0.07604480869688966</v>
+        <v>-0.7008594408362938</v>
       </c>
       <c r="G24">
-        <v>-2.747475862438121</v>
+        <v>-0.8717505547969192</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.13570432769319</v>
       </c>
       <c r="E25">
-        <v>-29.0952437946593</v>
+        <v>-25.2106191644515</v>
       </c>
       <c r="F25">
-        <v>-0.4131475610263584</v>
+        <v>-1.214957504892112</v>
       </c>
       <c r="G25">
-        <v>-2.219937120209718</v>
+        <v>-1.348002325530933</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.41773357788251</v>
       </c>
       <c r="E26">
-        <v>-28.74547351925486</v>
+        <v>-24.95110590449394</v>
       </c>
       <c r="F26">
-        <v>0.06340806396718321</v>
+        <v>-0.9017849245897307</v>
       </c>
       <c r="G26">
-        <v>-2.686796873248819</v>
+        <v>-1.667638807893105</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.66973520029787</v>
       </c>
       <c r="E27">
-        <v>-26.04546599013557</v>
+        <v>-24.910403980113</v>
       </c>
       <c r="F27">
-        <v>-0.5349208827074969</v>
+        <v>-0.828265660856469</v>
       </c>
       <c r="G27">
-        <v>-4.879834660283624</v>
+        <v>-1.957447274946444</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.87059770497342</v>
       </c>
       <c r="E28">
-        <v>-28.8145146339758</v>
+        <v>-25.06782732204164</v>
       </c>
       <c r="F28">
-        <v>-0.178125646606291</v>
+        <v>-0.9225562372149283</v>
       </c>
       <c r="G28">
-        <v>-2.948879521410761</v>
+        <v>-1.906706543466035</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.99663031858562</v>
       </c>
       <c r="E29">
-        <v>-26.0153154101925</v>
+        <v>-25.02021041785099</v>
       </c>
       <c r="F29">
-        <v>-0.549434707971947</v>
+        <v>-0.7281417212474955</v>
       </c>
       <c r="G29">
-        <v>-3.055929321968635</v>
+        <v>-1.638989346796252</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.05495867111132</v>
       </c>
       <c r="E30">
-        <v>-27.82650576040431</v>
+        <v>-25.45805951270462</v>
       </c>
       <c r="F30">
-        <v>0.1807736426980256</v>
+        <v>-0.8116983128004789</v>
       </c>
       <c r="G30">
-        <v>-3.401947541733259</v>
+        <v>-2.410624543271738</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.05127497650098</v>
       </c>
       <c r="E31">
-        <v>-26.85234496034827</v>
+        <v>-24.35244616915392</v>
       </c>
       <c r="F31">
-        <v>-0.14574227972865</v>
+        <v>-0.7609268463154945</v>
       </c>
       <c r="G31">
-        <v>-4.577499088909683</v>
+        <v>-2.283492973472646</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.98359339641671</v>
       </c>
       <c r="E32">
-        <v>-27.94072746029978</v>
+        <v>-24.32987625469969</v>
       </c>
       <c r="F32">
-        <v>-0.2503029551470176</v>
+        <v>-0.500537008552095</v>
       </c>
       <c r="G32">
-        <v>-3.850437077574945</v>
+        <v>-1.840760476323753</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.87040076167886</v>
       </c>
       <c r="E33">
-        <v>-26.32986321476529</v>
+        <v>-24.56381722193595</v>
       </c>
       <c r="F33">
-        <v>-0.3971592417849251</v>
+        <v>-0.4281145032601398</v>
       </c>
       <c r="G33">
-        <v>-3.2380556742661</v>
+        <v>-2.44890438134233</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.73169110443543</v>
       </c>
       <c r="E34">
-        <v>-27.53524789765297</v>
+        <v>-23.75926135888918</v>
       </c>
       <c r="F34">
-        <v>-0.2894250908464326</v>
+        <v>-0.4269829533879157</v>
       </c>
       <c r="G34">
-        <v>-3.236949952055983</v>
+        <v>-1.740149686839762</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.57452390094489</v>
       </c>
       <c r="E35">
-        <v>-26.85697306078411</v>
+        <v>-23.6612108396751</v>
       </c>
       <c r="F35">
-        <v>-0.2872912164168211</v>
+        <v>-0.4637624660722138</v>
       </c>
       <c r="G35">
-        <v>-4.111486835528635</v>
+        <v>-2.631749122021818</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.40834214086013</v>
       </c>
       <c r="E36">
-        <v>-26.73597676377316</v>
+        <v>-23.58537701394266</v>
       </c>
       <c r="F36">
-        <v>-0.1361390164279953</v>
+        <v>-0.523950813192223</v>
       </c>
       <c r="G36">
-        <v>-4.448166006326975</v>
+        <v>-3.060017845709635</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.2522370154958</v>
       </c>
       <c r="E37">
-        <v>-24.75045374968807</v>
+        <v>-23.83530349442598</v>
       </c>
       <c r="F37">
-        <v>-0.1586018552897095</v>
+        <v>-0.4264677088633744</v>
       </c>
       <c r="G37">
-        <v>-3.949697164478913</v>
+        <v>-3.007373550544144</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.10876470831958</v>
       </c>
       <c r="E38">
-        <v>-25.68173895783949</v>
+        <v>-22.21998775894195</v>
       </c>
       <c r="F38">
-        <v>0.1267897674249846</v>
+        <v>-0.550939023175431</v>
       </c>
       <c r="G38">
-        <v>-3.266774656819277</v>
+        <v>-1.679851410387477</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.970815845099768</v>
       </c>
       <c r="E39">
-        <v>-24.25349448361232</v>
+        <v>-22.24598572821999</v>
       </c>
       <c r="F39">
-        <v>-0.3051085708836356</v>
+        <v>-0.43244355130717</v>
       </c>
       <c r="G39">
-        <v>-4.322100432191529</v>
+        <v>-1.201835118881031</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.851518847741634</v>
       </c>
       <c r="E40">
-        <v>-23.77334038457903</v>
+        <v>-22.68545148829436</v>
       </c>
       <c r="F40">
-        <v>-0.5328855839988185</v>
+        <v>-0.7257005225114455</v>
       </c>
       <c r="G40">
-        <v>-4.232209189163698</v>
+        <v>-2.297513133831459</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.748177067547905</v>
       </c>
       <c r="E41">
-        <v>-22.99427530172144</v>
+        <v>-21.69792716144168</v>
       </c>
       <c r="F41">
-        <v>-0.2273629766612908</v>
+        <v>-0.2316406659293475</v>
       </c>
       <c r="G41">
-        <v>-3.908116712505667</v>
+        <v>-1.822185005302902</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.645602931343433</v>
       </c>
       <c r="E42">
-        <v>-24.51694751595656</v>
+        <v>-20.19040722123624</v>
       </c>
       <c r="F42">
-        <v>-0.0406431654984627</v>
+        <v>-0.38978097332819</v>
       </c>
       <c r="G42">
-        <v>-4.796014957774816</v>
+        <v>-2.51122871166465</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.550922184602893</v>
       </c>
       <c r="E43">
-        <v>-22.09253838647008</v>
+        <v>-20.48146583113123</v>
       </c>
       <c r="F43">
-        <v>0.1279130336231807</v>
+        <v>-0.369647503603148</v>
       </c>
       <c r="G43">
-        <v>-4.344545930947787</v>
+        <v>-2.645206489638955</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.464038188687629</v>
       </c>
       <c r="E44">
-        <v>-23.76671975557982</v>
+        <v>-19.98627266991847</v>
       </c>
       <c r="F44">
-        <v>-0.1738603828492764</v>
+        <v>-0.5397403242569844</v>
       </c>
       <c r="G44">
-        <v>-3.528973174075094</v>
+        <v>-2.534005264974836</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.372511092123808</v>
       </c>
       <c r="E45">
-        <v>-21.20713114849037</v>
+        <v>-18.49053581908098</v>
       </c>
       <c r="F45">
-        <v>-0.03966652033056208</v>
+        <v>-0.6273691699621301</v>
       </c>
       <c r="G45">
-        <v>-4.053678089321881</v>
+        <v>-2.155937653844527</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.280217083928644</v>
       </c>
       <c r="E46">
-        <v>-20.27203296522449</v>
+        <v>-18.48495673910353</v>
       </c>
       <c r="F46">
-        <v>-0.4758491748464613</v>
+        <v>-0.1814233772368359</v>
       </c>
       <c r="G46">
-        <v>-3.657078044262732</v>
+        <v>-2.393797040295623</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.193910423347566</v>
       </c>
       <c r="E47">
-        <v>-20.39605881134657</v>
+        <v>-18.48203587336858</v>
       </c>
       <c r="F47">
-        <v>0.0074535026428822</v>
+        <v>-0.1360868292816189</v>
       </c>
       <c r="G47">
-        <v>-4.586298518953066</v>
+        <v>-2.737640231640946</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.108560904037821</v>
       </c>
       <c r="E48">
-        <v>-19.52992928721751</v>
+        <v>-17.75342704790446</v>
       </c>
       <c r="F48">
-        <v>0.3667296991154726</v>
+        <v>-0.3773695445320449</v>
       </c>
       <c r="G48">
-        <v>-4.177201164483168</v>
+        <v>-2.847341779175775</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.02255721428169</v>
       </c>
       <c r="E49">
-        <v>-20.81559928578719</v>
+        <v>-18.23141653636209</v>
       </c>
       <c r="F49">
-        <v>-0.1901386306816895</v>
+        <v>-0.3047656267788766</v>
       </c>
       <c r="G49">
-        <v>-3.593760550278632</v>
+        <v>-2.446623415465773</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.94809494345601</v>
       </c>
       <c r="E50">
-        <v>-18.08487058899987</v>
+        <v>-16.66145799653888</v>
       </c>
       <c r="F50">
-        <v>0.2821119689195031</v>
+        <v>-0.1909802519629338</v>
       </c>
       <c r="G50">
-        <v>-4.856882648059857</v>
+        <v>-2.050059786407556</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.883935506405285</v>
       </c>
       <c r="E51">
-        <v>-19.28351237409013</v>
+        <v>-16.57860050762054</v>
       </c>
       <c r="F51">
-        <v>0.02308479553370887</v>
+        <v>-0.3151873170734972</v>
       </c>
       <c r="G51">
-        <v>-5.400864869981819</v>
+        <v>-3.159933420630378</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.822060613953644</v>
       </c>
       <c r="E52">
-        <v>-18.58303895763567</v>
+        <v>-15.34713634292267</v>
       </c>
       <c r="F52">
-        <v>0.1060408207196626</v>
+        <v>-0.2257493169606374</v>
       </c>
       <c r="G52">
-        <v>-4.976505900575882</v>
+        <v>-1.989145748484966</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.775161141981314</v>
       </c>
       <c r="E53">
-        <v>-17.97896316738248</v>
+        <v>-14.67878339260461</v>
       </c>
       <c r="F53">
-        <v>0.3504696753659211</v>
+        <v>-0.516650411271351</v>
       </c>
       <c r="G53">
-        <v>-3.824505574365833</v>
+        <v>-2.254045670900828</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.743668119422516</v>
       </c>
       <c r="E54">
-        <v>-16.1930009458674</v>
+        <v>-15.16099794731139</v>
       </c>
       <c r="F54">
-        <v>0.1904092123273894</v>
+        <v>-0.4226646741171219</v>
       </c>
       <c r="G54">
-        <v>-5.415338575079513</v>
+        <v>-2.634228720630732</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.716346876450363</v>
       </c>
       <c r="E55">
-        <v>-16.75674614660828</v>
+        <v>-15.3732475240509</v>
       </c>
       <c r="F55">
-        <v>-0.2549252452546388</v>
+        <v>0.1106349463355886</v>
       </c>
       <c r="G55">
-        <v>-4.360231295712854</v>
+        <v>-3.032656186827558</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.702223612401061</v>
       </c>
       <c r="E56">
-        <v>-15.91944941648606</v>
+        <v>-14.13044858891184</v>
       </c>
       <c r="F56">
-        <v>0.168257011241725</v>
+        <v>-0.2839719482338035</v>
       </c>
       <c r="G56">
-        <v>-5.516492294031944</v>
+        <v>-3.025399471005476</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.70337492866901</v>
       </c>
       <c r="E57">
-        <v>-16.94797454700418</v>
+        <v>-13.57780720643777</v>
       </c>
       <c r="F57">
-        <v>-0.1387889637495509</v>
+        <v>-0.4833873182119369</v>
       </c>
       <c r="G57">
-        <v>-5.490180078085817</v>
+        <v>-3.19676323975477</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.709103559551142</v>
       </c>
       <c r="E58">
-        <v>-15.52982856981412</v>
+        <v>-12.99815800498196</v>
       </c>
       <c r="F58">
-        <v>-0.3681373898278444</v>
+        <v>-0.2836712508665872</v>
       </c>
       <c r="G58">
-        <v>-5.549303110871661</v>
+        <v>-2.231696177965209</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.721258256497277</v>
       </c>
       <c r="E59">
-        <v>-15.88020566073559</v>
+        <v>-12.54298749704899</v>
       </c>
       <c r="F59">
-        <v>-0.5698315985310792</v>
+        <v>-0.3631464762259774</v>
       </c>
       <c r="G59">
-        <v>-5.083734470592876</v>
+        <v>-2.564515252664759</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.744182668537713</v>
       </c>
       <c r="E60">
-        <v>-15.03041939930022</v>
+        <v>-12.98042902924193</v>
       </c>
       <c r="F60">
-        <v>-0.5093483526156733</v>
+        <v>-0.3395984760665959</v>
       </c>
       <c r="G60">
-        <v>-4.935382303887055</v>
+        <v>-2.985805346355793</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.770087506967981</v>
       </c>
       <c r="E61">
-        <v>-14.05899832601882</v>
+        <v>-12.85911121057644</v>
       </c>
       <c r="F61">
-        <v>-0.2137760945205734</v>
+        <v>-0.08541062504795638</v>
       </c>
       <c r="G61">
-        <v>-4.588125940090744</v>
+        <v>-3.507434764796596</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.792661731947284</v>
       </c>
       <c r="E62">
-        <v>-14.97144961077233</v>
+        <v>-12.46428714726969</v>
       </c>
       <c r="F62">
-        <v>0.4139259318899744</v>
+        <v>-0.07963524751563822</v>
       </c>
       <c r="G62">
-        <v>-6.545787249828907</v>
+        <v>-2.711129382962462</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.819740544839894</v>
       </c>
       <c r="E63">
-        <v>-15.62201471518826</v>
+        <v>-12.35279611720084</v>
       </c>
       <c r="F63">
-        <v>0.3389180919338819</v>
+        <v>-0.1554905073247946</v>
       </c>
       <c r="G63">
-        <v>-5.069611683322345</v>
+        <v>-3.350167298953519</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.846832062847534</v>
       </c>
       <c r="E64">
-        <v>-12.63296374710739</v>
+        <v>-12.16882686063923</v>
       </c>
       <c r="F64">
-        <v>-0.1371338856787575</v>
+        <v>-0.5950827220706166</v>
       </c>
       <c r="G64">
-        <v>-4.416944251346108</v>
+        <v>-3.16342604617431</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.862836843175781</v>
       </c>
       <c r="E65">
-        <v>-13.82671478026937</v>
+        <v>-11.56926143049768</v>
       </c>
       <c r="F65">
-        <v>-0.1225446789806526</v>
+        <v>-0.4038541071343507</v>
       </c>
       <c r="G65">
-        <v>-4.963445798423457</v>
+        <v>-3.324090131740679</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.877469800376453</v>
       </c>
       <c r="E66">
-        <v>-14.59001624510626</v>
+        <v>-12.28455654237926</v>
       </c>
       <c r="F66">
-        <v>-0.263282643981483</v>
+        <v>-0.1733915268992919</v>
       </c>
       <c r="G66">
-        <v>-5.328512897221048</v>
+        <v>-2.801060352536764</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.891231294747158</v>
       </c>
       <c r="E67">
-        <v>-13.27349828159633</v>
+        <v>-10.91439427577447</v>
       </c>
       <c r="F67">
-        <v>-0.05174908726779567</v>
+        <v>-0.637971444350561</v>
       </c>
       <c r="G67">
-        <v>-5.342480088851233</v>
+        <v>-3.130916488978666</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.894041130377387</v>
       </c>
       <c r="E68">
-        <v>-13.96527702795607</v>
+        <v>-12.3612734205432</v>
       </c>
       <c r="F68">
-        <v>-0.440926033511837</v>
+        <v>-0.5473165725229887</v>
       </c>
       <c r="G68">
-        <v>-6.896244911161693</v>
+        <v>-3.044646982770799</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.896292950534685</v>
       </c>
       <c r="E69">
-        <v>-11.54692246821785</v>
+        <v>-10.22089470929181</v>
       </c>
       <c r="F69">
-        <v>-0.2042299885707119</v>
+        <v>-0.1893475398120159</v>
       </c>
       <c r="G69">
-        <v>-5.577025619217518</v>
+        <v>-2.965637502930552</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.902386369747786</v>
       </c>
       <c r="E70">
-        <v>-12.57263994485121</v>
+        <v>-11.85292504233816</v>
       </c>
       <c r="F70">
-        <v>-0.2494696175398013</v>
+        <v>-0.782186067340941</v>
       </c>
       <c r="G70">
-        <v>-4.98564631680981</v>
+        <v>-3.962661260810699</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.904105273489876</v>
       </c>
       <c r="E71">
-        <v>-13.14476282250628</v>
+        <v>-10.43386884187255</v>
       </c>
       <c r="F71">
-        <v>-0.6080077386564973</v>
+        <v>-0.703184668135952</v>
       </c>
       <c r="G71">
-        <v>-4.381958406087091</v>
+        <v>-3.414319050413515</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.903610253511694</v>
       </c>
       <c r="E72">
-        <v>-14.34831347342086</v>
+        <v>-11.14209500582815</v>
       </c>
       <c r="F72">
-        <v>-0.107069947528955</v>
+        <v>-1.026069027868755</v>
       </c>
       <c r="G72">
-        <v>-4.479149402029014</v>
+        <v>-3.358979971179058</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.90654106554485</v>
       </c>
       <c r="E73">
-        <v>-12.21616752791542</v>
+        <v>-11.49662017894065</v>
       </c>
       <c r="F73">
-        <v>-0.7890408075991069</v>
+        <v>-0.8911271495853124</v>
       </c>
       <c r="G73">
-        <v>-5.627230042320566</v>
+        <v>-2.890299418093358</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.906452633963582</v>
       </c>
       <c r="E74">
-        <v>-13.10245781832662</v>
+        <v>-11.48882667517344</v>
       </c>
       <c r="F74">
-        <v>-0.6497400600421336</v>
+        <v>-1.063324851809662</v>
       </c>
       <c r="G74">
-        <v>-4.732071770683794</v>
+        <v>-3.475782638895625</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.896287161830562</v>
       </c>
       <c r="E75">
-        <v>-14.25967765166873</v>
+        <v>-12.96788968471469</v>
       </c>
       <c r="F75">
-        <v>-0.8739318990380002</v>
+        <v>-1.120801124052906</v>
       </c>
       <c r="G75">
-        <v>-4.801646195737117</v>
+        <v>-2.882377282617882</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.883932005544159</v>
       </c>
       <c r="E76">
-        <v>-12.79765981829235</v>
+        <v>-11.99368812839258</v>
       </c>
       <c r="F76">
-        <v>-1.127340256330605</v>
+        <v>-0.9908261367166497</v>
       </c>
       <c r="G76">
-        <v>-5.911645630690431</v>
+        <v>-2.81865590207799</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.865071476356155</v>
       </c>
       <c r="E77">
-        <v>-16.13217901147038</v>
+        <v>-11.44030407618126</v>
       </c>
       <c r="F77">
-        <v>-0.7726656407805662</v>
+        <v>-1.141972538133656</v>
       </c>
       <c r="G77">
-        <v>-5.300681140872395</v>
+        <v>-2.859597418762157</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.829039986580124</v>
       </c>
       <c r="E78">
-        <v>-15.13995865707176</v>
+        <v>-13.11699874836525</v>
       </c>
       <c r="F78">
-        <v>-0.7417766486975754</v>
+        <v>-1.059027281723939</v>
       </c>
       <c r="G78">
-        <v>-4.774572554316958</v>
+        <v>-2.896645733892141</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.785879361654578</v>
       </c>
       <c r="E79">
-        <v>-16.14862642906624</v>
+        <v>-14.62004455625112</v>
       </c>
       <c r="F79">
-        <v>-0.6620206067886363</v>
+        <v>-1.599101290796743</v>
       </c>
       <c r="G79">
-        <v>-4.534524897264403</v>
+        <v>-2.317733945985327</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.737315813973742</v>
       </c>
       <c r="E80">
-        <v>-16.45726457505901</v>
+        <v>-14.24712472171947</v>
       </c>
       <c r="F80">
-        <v>-1.194360977788905</v>
+        <v>-1.558033320068152</v>
       </c>
       <c r="G80">
-        <v>-4.512940140348356</v>
+        <v>-2.526798207335842</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.674118711838851</v>
       </c>
       <c r="E81">
-        <v>-15.5369609163762</v>
+        <v>-14.56304012544257</v>
       </c>
       <c r="F81">
-        <v>-1.009673151865144</v>
+        <v>-1.538054755047434</v>
       </c>
       <c r="G81">
-        <v>-3.689776302554114</v>
+        <v>-2.622059155228371</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.607482321892128</v>
       </c>
       <c r="E82">
-        <v>-16.97623675328605</v>
+        <v>-14.68181747018975</v>
       </c>
       <c r="F82">
-        <v>-1.55490788985739</v>
+        <v>-1.392076537856494</v>
       </c>
       <c r="G82">
-        <v>-4.962462566398293</v>
+        <v>-2.038009400644609</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.545000478573309</v>
       </c>
       <c r="E83">
-        <v>-18.37216150852048</v>
+        <v>-16.07184162379219</v>
       </c>
       <c r="F83">
-        <v>-1.492595608716603</v>
+        <v>-1.728809543829298</v>
       </c>
       <c r="G83">
-        <v>-4.465026614758483</v>
+        <v>-2.255105045473395</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.482926209823306</v>
       </c>
       <c r="E84">
-        <v>-18.95985327981392</v>
+        <v>-17.45069403201769</v>
       </c>
       <c r="F84">
-        <v>-2.269111353937873</v>
+        <v>-1.851872633556596</v>
       </c>
       <c r="G84">
-        <v>-4.442879065100759</v>
+        <v>-2.310328255613978</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.428264578474899</v>
       </c>
       <c r="E85">
-        <v>-19.98288537136073</v>
+        <v>-17.84269232754366</v>
       </c>
       <c r="F85">
-        <v>-1.731673209940776</v>
+        <v>-2.161136976452569</v>
       </c>
       <c r="G85">
-        <v>-2.989433704266834</v>
+        <v>-2.329827368840285</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.394361412832691</v>
       </c>
       <c r="E86">
-        <v>-19.87044789022429</v>
+        <v>-18.87392548551837</v>
       </c>
       <c r="F86">
-        <v>-1.778526498610519</v>
+        <v>-2.036519041110217</v>
       </c>
       <c r="G86">
-        <v>-4.38137243952664</v>
+        <v>-2.209085151931987</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.382694417850763</v>
       </c>
       <c r="E87">
-        <v>-22.29686313369616</v>
+        <v>-20.64064622097485</v>
       </c>
       <c r="F87">
-        <v>-2.186207515898296</v>
+        <v>-2.093134639621952</v>
       </c>
       <c r="G87">
-        <v>-4.087670770919118</v>
+        <v>-2.397620720393481</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.392833435028484</v>
       </c>
       <c r="E88">
-        <v>-23.25971180568104</v>
+        <v>-21.84556899951376</v>
       </c>
       <c r="F88">
-        <v>-2.343955177148211</v>
+        <v>-2.147326435113095</v>
       </c>
       <c r="G88">
-        <v>-5.409525257112553</v>
+        <v>-1.796902369019488</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.441164764072857</v>
       </c>
       <c r="E89">
-        <v>-24.62230246374501</v>
+        <v>-23.2061354296963</v>
       </c>
       <c r="F89">
-        <v>-1.945820265810296</v>
+        <v>-2.442084408051243</v>
       </c>
       <c r="G89">
-        <v>-3.699191494067801</v>
+        <v>-2.894990461122505</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.529246904483539</v>
       </c>
       <c r="E90">
-        <v>-25.36491785931485</v>
+        <v>-24.8518417542458</v>
       </c>
       <c r="F90">
-        <v>-2.032624057582253</v>
+        <v>-2.845486079336158</v>
       </c>
       <c r="G90">
-        <v>-5.059901853255663</v>
+        <v>-2.006906825303156</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.647682599049045</v>
       </c>
       <c r="E91">
-        <v>-25.18721601077986</v>
+        <v>-26.05326855085079</v>
       </c>
       <c r="F91">
-        <v>-2.094371392154331</v>
+        <v>-2.962492974981588</v>
       </c>
       <c r="G91">
-        <v>-4.11823041679213</v>
+        <v>-3.21416015656364</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.806432255727577</v>
       </c>
       <c r="E92">
-        <v>-29.69088756631021</v>
+        <v>-27.65734461384778</v>
       </c>
       <c r="F92">
-        <v>-2.320791539463729</v>
+        <v>-2.974483593137111</v>
       </c>
       <c r="G92">
-        <v>-5.095516702167142</v>
+        <v>-3.568441497994286</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.002631894481549</v>
       </c>
       <c r="E93">
-        <v>-31.23708067454116</v>
+        <v>-30.25832573760434</v>
       </c>
       <c r="F93">
-        <v>-3.020999736273914</v>
+        <v>-3.087869694864904</v>
       </c>
       <c r="G93">
-        <v>-3.99599514384562</v>
+        <v>-2.996051484799837</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.216302871139323</v>
       </c>
       <c r="E94">
-        <v>-34.03109479558568</v>
+        <v>-31.47145411104514</v>
       </c>
       <c r="F94">
-        <v>-2.721770236095455</v>
+        <v>-2.932936826049702</v>
       </c>
       <c r="G94">
-        <v>-5.620509634875845</v>
+        <v>-3.270515573278654</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.44560568641824</v>
       </c>
       <c r="E95">
-        <v>-33.75541941189474</v>
+        <v>-33.78297517623141</v>
       </c>
       <c r="F95">
-        <v>-2.747027986574214</v>
+        <v>-2.998537725779603</v>
       </c>
       <c r="G95">
-        <v>-5.585642969256241</v>
+        <v>-3.598398624579151</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.680479649505596</v>
       </c>
       <c r="E96">
-        <v>-36.00355089792163</v>
+        <v>-35.62576974654275</v>
       </c>
       <c r="F96">
-        <v>-3.087399182180115</v>
+        <v>-3.663288484280359</v>
       </c>
       <c r="G96">
-        <v>-5.72337159532654</v>
+        <v>-3.684323834050935</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.897395365651198</v>
       </c>
       <c r="E97">
-        <v>-37.47832317834062</v>
+        <v>-38.66218628850685</v>
       </c>
       <c r="F97">
-        <v>-3.24003084635034</v>
+        <v>-3.786286961350238</v>
       </c>
       <c r="G97">
-        <v>-6.441233600607644</v>
+        <v>-3.572367805003861</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.07912456340614</v>
       </c>
       <c r="E98">
-        <v>-40.63220154335267</v>
+        <v>-39.65901210097128</v>
       </c>
       <c r="F98">
-        <v>-3.625779179914194</v>
+        <v>-3.973044049046192</v>
       </c>
       <c r="G98">
-        <v>-6.771182432324646</v>
+        <v>-4.379674129664994</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.21708477661469</v>
       </c>
       <c r="E99">
-        <v>-43.58902336192096</v>
+        <v>-42.60024011929415</v>
       </c>
       <c r="F99">
-        <v>-3.801575310136305</v>
+        <v>-4.008508114294844</v>
       </c>
       <c r="G99">
-        <v>-6.260626788712704</v>
+        <v>-4.945241108503005</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.2897159893603</v>
       </c>
       <c r="E100">
-        <v>-44.23296104462666</v>
+        <v>-44.5889262724736</v>
       </c>
       <c r="F100">
-        <v>-4.019950353229714</v>
+        <v>-4.205039937343832</v>
       </c>
       <c r="G100">
-        <v>-7.541092834574171</v>
+        <v>-5.243852316145266</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.28021027532556</v>
       </c>
       <c r="E101">
-        <v>-46.5347232483264</v>
+        <v>-46.30735309687528</v>
       </c>
       <c r="F101">
-        <v>-3.871990681211277</v>
+        <v>-3.904841247304097</v>
       </c>
       <c r="G101">
-        <v>-6.85964683022505</v>
+        <v>-5.355308452815909</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.1862611130522</v>
       </c>
       <c r="E102">
-        <v>-49.43529689124541</v>
+        <v>-48.57658500754092</v>
       </c>
       <c r="F102">
-        <v>-4.214692074321253</v>
+        <v>-4.885898299992024</v>
       </c>
       <c r="G102">
-        <v>-7.733438840951366</v>
+        <v>-5.64002199028431</v>
       </c>
     </row>
   </sheetData>
